--- a/output/full_scan/batch_seq7_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-12.xlsx
@@ -428,17 +428,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6654</v>
+        <v>6691</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>752.5760245077367</v>
+        <v>1439.221366378008</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>171.5</v>
+        <v>689</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>80.46472015195955</v>
+        <v>63.35037170870221</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45.04070150092064</v>
+        <v>12.25161941405056</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.2576024507736771</v>
+        <v>3.922136637800756</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.306292569714053</v>
+        <v>2.307448213434013</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6548</v>
+        <v>6613</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>752.2691627836514</v>
+        <v>1343.694916387367</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>88</v>
+        <v>311.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.00594908770033</v>
+        <v>73.95110552805787</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>44.50250952072402</v>
+        <v>26.78024024669412</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.2269162783651427</v>
+        <v>3.869491638736721</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,64 +623,6583 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.033515133735808</v>
+        <v>2.446840235084387</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
+        <v>6834</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>天二科技</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1105.072930166025</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>66.97500462086413</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>44.58795555777179</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>3.507293016602478</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>-0.4703940533548589</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>6585</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>鼎基</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1042.737637177067</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>84.80704409814558</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>52.3430172199513</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>2.273763717706697</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>3.404512998620722</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>6693</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>廣閎科</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>988.2555285882931</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>60.67326552464213</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>38.13051622662911</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1.325552858829318</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.8440851887111807</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6670</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>復盛應用</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>945.2791095760716</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>64.57715267769731</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>27.32572381330998</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1.027910957607156</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1.666814014261798</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6672</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>騰輝電子-KY</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>941.5115291927784</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>58.27472580265626</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>26.82420816479992</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.651152919277843</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.7234319579223492</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>6515</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>938.2317872165454</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>9590</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>55.8604893705045</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>28.28603690989007</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1.323178721654538</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>31.94645497110673</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>6666</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>羅麗芬-KY</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>915.8001160444256</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>64.95111206162859</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>23.22456201374692</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1.580011604442551</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.3673178611625193</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>建德工業</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>913.2960952721388</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>60.40801380674862</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>21.63994280522896</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.8296095272138985</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>-0.0315490865075004</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>6494</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>九齊</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>879.0735539039327</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>56.69920501234039</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>26.32783324450461</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1.407355390393278</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>-0.2966379003442101</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>6579</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>研揚</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>854.7634772152513</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>57.72249178099449</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>37.98886845973424</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.4763477215251346</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>-1.860312208092697</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>6556</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>勝品</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>851.0357595140484</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>59.69841315770153</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>40.40427551846406</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.6035759514048381</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.028194378965658</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6821</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>聯寶</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>848.5983053794708</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>58.92484296255014</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>27.50835099401263</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>2.859830537947082</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>-0.3237379537184441</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>6684</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>安格</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>847.2108672084934</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>60.15206106605675</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>22.21880827809373</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.7210867208493389</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.4972067216379808</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>6757</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>台灣虎航-創</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>835.227024654462</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>58.63150805761379</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>24.65103432125978</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1.022702465446201</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>-0.0650093982742934</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>6525</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>捷敏-KY</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>808.670043365829</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>62.28865773771665</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>26.62249525061028</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1.3670043365829</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>-1.149425658495076</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>6831</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>邁科</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>800.7147558253639</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>727</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>54.47638520201185</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>29.44735732794548</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.5714755825363872</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>-14.55953599580587</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>6510</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>767.4814070183686</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>53.78316857944371</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>20.2238342542197</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1.248140701836861</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>25.03938460410083</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>6667</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>信紘科</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>760.5257221794232</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>52.36206606816729</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>16.84875673393351</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.5525722179423138</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>-0.3405663301232335</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>6625</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>必應</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>754.5471527858449</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>67.74840014312406</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>20.61544763007293</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1.454715278584495</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.5736951420212004</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>6654</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>天正國際</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>752.5760245077367</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>80.46472015195955</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>45.04070150092064</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.2576024507736771</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>1.306292569714053</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>6548</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>長科*</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>752.2691627836514</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>67.00594908770033</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>44.50250952072402</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.2269162783651427</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>1.033515133735808</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>6592</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>和潤企業</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>742.8405873602951</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>60.42256578213127</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>28.65069286648987</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.7840587360295079</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0.53723533918841</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>6491</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>晶碩</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>737.5423075838499</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>55.0654480803446</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>34.3332815675027</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.7542307583849934</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>-1.015695075438693</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>6756</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>威鋒電子</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>730.6638189799498</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>50.95179150283737</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>30.3866490886569</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.5663818979949837</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>-1.47888228601655</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>6598</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ABC-KY</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>709.6707148041402</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>56.20494059159515</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>28.32307820336339</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.4670714804140129</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>-0.0419988690738708</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>6811</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>宏碁資訊</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>699.3644799371708</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>55.76055458355348</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>28.12076516880447</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.4364479937170796</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>-0.8462737674239493</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>6792</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>詠業</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>684.9933402053592</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>52.73811702237706</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>37.25013753392933</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.4993340205359279</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>-0.7432289479537149</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>6698</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>旭暉應材</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>663.1729033366731</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>53.8426196014759</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>36.57107164100541</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.3172903336673161</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>-0.3209333130435352</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
         <v>6488</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>環球晶</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="C32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D32" s="2" t="n">
         <v>662.5458371040457</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E32" s="2" t="n">
         <v>864</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
         <v>56.65974066377529</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I32" s="2" t="n">
         <v>22.36898300906099</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J32" s="2" t="n">
         <v>0.2545837104045744</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N4" s="2" t="n">
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" s="2" t="n">
         <v>-17.74700922377546</v>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>6719</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>力智</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>652.6595723008693</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>48.95654425619204</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>44.33791469534564</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.2659572300869239</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>-5.562590038960765</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>6517</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>保勝光學</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>652.392326222285</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>57.1665956167943</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>27.43225059612823</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>2.739232622228495</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0.5981459935884297</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>6570</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>維田</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>650.8031252206774</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>59.77254341092335</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>26.9166361236684</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.5803125220677403</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-0.6655729637598826</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>6651</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>全宇昕</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>648.8858167046538</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>52.14167399444454</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>34.6185157097875</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.3885816704653897</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>-2.950196966813663</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>6645</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>金萬林-創</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>648.1006352770632</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>64.90101592564318</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>32.31940522847853</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>1.310063527706323</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0.2513482919771603</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>6589</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>台康生技</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>645.9019786625693</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>50.65700329549494</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>22.6679157040895</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.5901978662569263</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0.4747154919960829</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>6642</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>富致</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>639.1897080269429</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>55.53310866169349</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>50.48535183839749</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.4189708026942879</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>-1.223512062722292</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>6546</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>正基</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>603.3402689441103</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>47.96174772500873</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>21.20110146576823</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.3340268944110297</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>-1.112766244970513</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>6829</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>千附精密</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>600.8245195008677</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>46.60391911769435</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>19.06212519924883</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.5824519500867729</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>-3.549315092358835</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>6605</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>帝寶</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>584.8638308245222</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>55.14067556295032</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>24.25758543903784</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.486383082452225</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0.2251675362661762</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>6789</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>采鈺</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>582.0898951192012</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>481.5</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>43.2512782530456</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>20.11531736264052</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.7089895119201105</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>-11.18862285771298</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>6680</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>鑫創電子</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>580.2151898734177</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>51.57687357115028</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>8.177603659249908</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>2.521518987341772</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-2.088633093048997</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>6531</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>575.7228081680405</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>932</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>47.45569100974881</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>26.21777000390197</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.5722808168040465</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>-33.45027429296295</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>6690</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>安碁資訊</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>573.9901359742596</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>52.58693386197238</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>20.8510034838432</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1.399013597425967</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>-0.4135000890572087</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>6658</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>聯策</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>570.8810970695561</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>44.89151977327095</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>40.64749410518068</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.5881097069556086</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>-7.881722618659072</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>6716</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>應廣</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>564.5636299120681</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>45.59213573547009</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>34.06645631654469</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.4563629912068122</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>-2.760443362193044</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>6669</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>564.2916378359471</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>4850</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>43.40036561299445</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>22.725692198122</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.9291637835947152</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>-103.3916907951734</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>6805</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>563.7958297853377</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1825</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>46.91564593638572</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>15.67032824561152</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.8795829785337754</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>-15.76731125583796</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>6526</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>達發</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>562.8539316896206</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>633</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>46.49856695574925</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>18.9411600212376</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0.2853931689620547</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>-12.98589358143292</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>6763</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>綠界科技</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>561.0552387367616</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>57.29975266106455</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>25.54139702538401</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.60552387367615</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0.513814865460392</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>6788</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>華景電</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>545.4950742719509</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>49.19460400248141</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>11.23759351473349</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>1.049507427195091</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>-0.2415158755552601</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>6768</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>志強-KY</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>529.3554342984144</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>54.70982249502863</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>24.57660021993369</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.935543429841438</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0.4542332045452708</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>6512</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>啟發電</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>526.6321217361667</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>52.36920026014556</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>5.911962760106038</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.6632121736166775</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0.0685414516506359</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>6597</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>立誠</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>521.8380708713519</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>49.37661962781556</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>12.81085826791085</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.6838070871351836</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>-1.098763745639067</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>6668</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>中揚光</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>519.4283909044036</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>49.79220317319079</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>26.71884541123137</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.4428390904403546</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>-0.3072782284817903</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>6498</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>久禾光</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>514.1560332362419</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>46.44517605790305</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>29.99651366647329</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.4156033236241881</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>-1.166016209500364</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>6742</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>澤米</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>510.7075396907141</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>48.11915252893135</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>35.92467703639542</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.5707539690714033</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>-1.10552091339119</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>6532</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>瑞耘</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>509.2438089411345</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>42.10265693666164</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>22.91734190435798</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0.4243808941134514</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>-2.022874381984886</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>6735</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>美達科技</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>508.2680482709229</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>39.68087870212055</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>20.96610303302254</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.3268048270922885</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>-2.654046584841903</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>6761</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>穩得</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>507.67832865508</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>45.21659418919258</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>24.40252175594362</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.2678328655079979</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>-2.451562530512254</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>6695</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>芯鼎</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>502.1113160451625</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>46.20428115430055</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>25.57560206181457</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.2111316045162621</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>-1.243346258314066</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>6581</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>鋼聯</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>492.5864174424242</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>52.25893329713213</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>12.78344425100876</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.2586417442424168</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>-0.055099372385292</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>6505</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>481.1424424836221</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>50.16808277476873</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>14.07561188610444</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.6142442483622089</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>-0.0041492022471386</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>6840</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>東研信超</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>479.1672047976848</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>51.75859208884497</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>19.54206511084317</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.4167204797684722</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0.0203002668135018</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>6790</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>永豐實</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>478.3415831853125</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>50.79785433227166</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>14.5214021550435</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.8341583185312523</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0.0361937583789387</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>6781</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>AES-KY</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>478.1811518884475</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1145</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>49.63762302090735</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>13.73770392735597</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.8181151888447532</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>-7.933351130968696</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>6706</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>惠特</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>475.1373996284708</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>45.44262441353825</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>22.36519026262853</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>1.013739962847086</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>-5.942435776148383</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>6720</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>久昌</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>467.0174326872307</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>40.52307160250571</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>29.37418386912381</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>1.701743268723073</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0.2629288976941977</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>6534</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>正瀚-創</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>457.6341338704197</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>39.25559386739774</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>16.2648046122588</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.2634133870419619</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>-0.5787530688384424</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>6803</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>崑鼎</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>444.581553744779</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>52.76427001385105</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>20.54654471552102</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.4581553744779025</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0.2356214716549104</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>6577</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>勁豐</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>443.150136925321</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>50.23962001129429</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>13.13141559676797</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.8150136925321049</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-0.1441564081256232</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>6538</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>倉和</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>439.9479073519694</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>42.57933049912814</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>39.32751119829831</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.4947907351969416</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>-5.045702315905707</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>6725</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>矽科宏晟</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>439.4465451967516</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>39.91318917835019</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>16.62527288055928</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.4446545196751592</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>-4.902687506993615</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>6573</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>虹揚-KY</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>438.9284898759337</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>50.14137732558691</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>15.74869765195773</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.3928489875933674</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>-0.1458989299583265</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>6641</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>基士德-KY</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>436.9958112580093</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>48.49490369077849</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>19.87968205224712</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.6995811258009268</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>-0.0088074261618304</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>6715</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>嘉基</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>434.9793069394556</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>42.31091326738201</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>23.16714667046929</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.497930693945564</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>-11.78991338669432</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>6743</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>安普新</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>429.3169211907812</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>48.31901987002738</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>23.80706240214526</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1.431692119078114</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-0.1949188045703139</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>6614</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>425.6582175271963</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>48.82386107845721</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>11.8860772744966</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>1.065821752719626</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.1312034268847282</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>6754</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>匯僑設計</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>416.1587073224381</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>50.09880403299931</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>21.64506510419005</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.6158707322438157</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0.0393476786535822</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>6679</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>鈺太</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>412.2506625879463</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>39.1895969616655</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>27.73008400009535</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.2250662587946274</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-7.045084505490188</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>6664</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>群翊</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>408.0412511600979</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>36.78254951941623</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>23.10328626672168</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.3041251160097865</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-8.820433612814597</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>6584</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>404.5842300312814</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>40.57023162851407</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>13.03790041954738</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.4584230031281394</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-13.90060534095607</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>6782</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>視陽</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>404.3080260394906</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>46.28656693710408</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>10.2095205087155</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.4308026039490564</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.5644329037632123</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>6799</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>來頡</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>403.2779871882066</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>38.70575486505143</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>34.34008660844145</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.3277987188206648</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-2.899765831401588</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6776</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>展碁國際</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>401.2488834612473</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>50.87379043725076</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>11.23371571298776</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.6248883461247342</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.0225117482176466</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6741</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>91APP*-KY</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>376.9510376099445</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>47.62584923967975</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>12.08359955888562</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.6951037609944519</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>-0.1669665497385297</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6582</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>申豐</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>374.9236742020545</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>53.15998241994541</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>21.93053144069051</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.492367420205457</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.0521510107973183</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>6591</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>動力-KY</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>373.9439237735078</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>46.71509230387012</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>22.26856665412213</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.3943923773507808</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-0.0295693655466036</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>6486</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>互動</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>364.8750285419753</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>42.71968877708849</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>21.42589010370338</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.4875028541975337</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>0.0648897479006996</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>6806</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>森崴能源</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>359.2921863408052</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>31.90654378221178</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>30.99666397998374</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.4292186340805172</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>0.3543742169312498</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>6796</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>晉弘</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>350.4606801793023</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>37.50204378798177</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>33.23532302869783</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.546068017930228</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>0.0679198204262037</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>6588</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>東典光電</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>344.168681724904</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>35.54215913263459</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>20.50098875528046</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.9168681724904042</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-1.588524280213617</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6560</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>欣普羅</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>343.2712129146701</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>40.92673478009271</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>15.56015481958014</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.8271212914670065</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-0.1896645402495086</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>6753</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>龍德造船</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>342.7867770384262</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>38.7265374577003</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>13.05630213151427</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.2786777038426252</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.2731200319669602</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>6727</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>亞泰金屬</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>340.2137905907762</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>38.2904243202285</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>24.34106668050701</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.5213790590776215</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-25.44031596406248</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>6533</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>晶心科</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>338.3795427271071</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>40.56046524725676</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>20.96860127374476</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.3379542727107101</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-3.895956947657988</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6739</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>337.6082237530265</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>42.70609586530189</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>13.00438322937508</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.7608223753026472</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-10.58167931324792</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6530</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>創威</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>334.5894555986209</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>41.74771925044959</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>14.00912796952439</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.4589455598620885</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-1.802423777776995</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6689</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>伊雲谷</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>328.3766201353398</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>44.23292442507556</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>16.35415914732986</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.3376620135339795</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.1166041021153721</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>6558</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>興能高</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>327.7220224421057</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>45.28762453691233</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>30.98027017047518</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.2722022442105728</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.3778172842952344</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>6550</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>北極星藥業-KY</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>324.6219814927831</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>32.02842565642543</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>36.70445675178912</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.4621981492783083</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>0.0787579622125012</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>6708</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>天擎</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>307.1835851701961</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>42.85298511199251</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>15.99805650069054</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.2183585170196137</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-0.2069758632277131</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>6732</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>昇佳電子</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>302.9834591474245</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>38.17081093300406</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>25.31596515884792</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.2983459147424511</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-3.187205407847617</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>6771</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>平和環保-創</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>289.1349554563369</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>45.32758058682212</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>18.03816551999384</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.9134955456336898</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>0.0988056528788671</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, cci_momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>6640</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>285.6697093138958</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>34.65905129818704</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>26.66259027819535</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.566970931389577</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-29.50388463613598</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>6541</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>泰福-KY</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>285.4083847067454</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>47.38488594806845</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>17.35437898483762</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.5408384706745388</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.0120363957732418</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>6807</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>峰源-KY</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>282.7974897025914</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>42.17555397773148</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>26.80314266072943</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.7797489702591379</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.2722332480637313</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>6830</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>汎銓</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>280.1480886728596</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>32.05321326489768</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>18.92944573009581</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1.014808867285957</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>-23.75395925585467</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6823</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>濾能</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>278.4190675883651</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>29.50880640363182</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>22.56580683122496</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.3419067588365156</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>-1.156191030053747</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6643</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>269.8169096361333</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>472</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>33.8375275201508</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>23.993351329605</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.4816909636133307</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-15.8073570539635</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6568</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>宏觀</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>268.7133425042414</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>34.89053250460802</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>24.55747221299236</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.3713342504241423</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-5.544018983341582</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>6552</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>易華電</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>268.0338728068227</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>45.62034853849859</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>18.94188699733569</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.303387280682273</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.6755486153582034</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6838</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>台新藥</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>260.5630778467592</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>33.87017950631197</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>12.4359650171781</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.5563077846759226</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.026731542109003</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6683</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>雍智科技</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>255.9980697857496</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>38.02740809136308</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>19.43003087051283</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5998069785749578</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-35.93674722678978</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6835</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>圓裕</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>216.5139668567862</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>40.21757428699651</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>11.84936842105753</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.1513966856786202</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.2202401640833645</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>6692</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>進能服</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>215.9797119328594</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>31.17327505361293</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>25.54810292523056</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.5979711932859375</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.0357561056390496</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>6624</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>萬年清</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>213.2826100753282</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>49.76517388607422</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>12.78802328932573</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.3282610075328188</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>1.196900092629635</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>6561</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>是方</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>207.9446475864849</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>39.81324753269506</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>15.41020811668674</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.7944647586484911</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>-2.461666938478563</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>6794</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>向榮生技-創</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>201.3158945401392</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>44.57433337164276</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>12.33269621905639</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>1.131589454013918</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.0613888653100068</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>南六</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>194.8079518610697</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>29.69263671653396</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>17.69284032437168</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.4807951861069746</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-0.0926751667173485</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>6655</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>科定</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>190.8118048262243</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>29.24051523655247</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>14.15471623079107</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.08118048262242961</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-1.19232648510111</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>6722</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>輝創</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>163.9222535835045</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>49.17416285415418</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>15.70589858380092</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.3922253583504528</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.07366923592527851</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6657</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>華安</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>158.5903182956462</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>33.41985837213251</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>17.38870414897994</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.8590318295646184</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.4162624397911492</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6671</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>三能-KY</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>68.01455048315172</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>29.37125706602235</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>14.79088887781482</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.8014550483151721</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0122163748732506</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6674</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>鋐寶科技</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>62.20726189162345</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>41.07953107765963</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>19.02671384896492</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.2207261891623441</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.06612593847954019</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq7_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-12.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.35037170870221</v>
+        <v>63.3503716479911</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.25161941405056</v>
+        <v>12.25161946025641</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.922136637800756</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.307448213434013</v>
+        <v>2.30744821286166</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1343.694916387367</v>
+        <v>1358.694916387367</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>311.5</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>73.95110552805787</v>
+        <v>73.95110553675823</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26.78024024669412</v>
+        <v>26.78024036685591</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>3.869491638736721</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.446840235084387</v>
+        <v>2.446840234225824</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1105.072930166025</v>
+        <v>1120.072930166025</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>84.09999999999999</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.97500462086413</v>
+        <v>66.97500462743406</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>44.58795555777179</v>
+        <v>44.58795546463653</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3.507293016602478</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.4703940533548589</v>
+        <v>-0.470394053068671</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1042.737637177067</v>
+        <v>1057.737637177067</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>136</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>84.80704409814558</v>
+        <v>84.80704416041561</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>52.3430172199513</v>
+        <v>52.34301727655822</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.273763717706697</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.404512998620722</v>
+        <v>3.404512997571366</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>988.2555285882931</v>
+        <v>1003.255528588293</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>169</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>60.67326552464213</v>
+        <v>60.67326555193848</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38.13051622662911</v>
+        <v>38.13051634098067</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.325552858829318</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.8440851887111807</v>
+        <v>0.8440851882151543</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6670</v>
+        <v>6488</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>945.2791095760716</v>
+        <v>997.5458371040456</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>285</v>
+        <v>864</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>64.57715267769731</v>
+        <v>56.65974068375574</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27.32572381330998</v>
+        <v>22.36898317029963</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.027910957607156</v>
+        <v>0.2545837104045744</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.666814014261798</v>
+        <v>-17.74700922596963</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6672</v>
+        <v>6670</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>941.5115291927784</v>
+        <v>960.2791095760716</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>221</v>
+        <v>285</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>58.27472580265626</v>
+        <v>64.57715267769731</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.82420816479992</v>
+        <v>27.32572379439813</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.651152919277843</v>
+        <v>1.027910957607156</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.7234319579223492</v>
+        <v>1.666814013307784</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6515</v>
+        <v>6672</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>938.2317872165454</v>
+        <v>956.5115291927784</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>9590</v>
+        <v>221</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.8604893705045</v>
+        <v>58.27472581000394</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28.28603690989007</v>
+        <v>26.82420822161101</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.323178721654538</v>
+        <v>0.651152919277843</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>31.94645497110673</v>
+        <v>-0.7234319582276161</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6666</v>
+        <v>6515</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>915.8001160444256</v>
+        <v>953.2317872165454</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>43.6</v>
+        <v>9590</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.95111206162859</v>
+        <v>55.86048937297496</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>23.22456201374692</v>
+        <v>28.28603701394127</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.580011604442551</v>
+        <v>1.323178721654538</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.3673178611625193</v>
+        <v>31.94645496080429</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6606</v>
+        <v>6666</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>913.2960952721388</v>
+        <v>930.8001160444256</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>26.2</v>
+        <v>43.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.40801380674862</v>
+        <v>64.9511121770654</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.63994280522896</v>
+        <v>23.22456208778748</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8296095272138985</v>
+        <v>1.580011604442551</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.0315490865075004</v>
+        <v>0.3673178608667901</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6494</v>
+        <v>6606</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>879.0735539039327</v>
+        <v>913.2960952721388</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.9</v>
+        <v>26.2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.69920501234039</v>
+        <v>60.40801379250701</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>26.32783324450461</v>
+        <v>21.63994297499591</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.407355390393278</v>
+        <v>0.8296095272138985</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>3</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.2966379003442101</v>
+        <v>-0.0315490865456588</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6579</v>
+        <v>6494</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>854.7634772152513</v>
+        <v>879.0735539039327</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>163</v>
+        <v>57.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.72249178099449</v>
+        <v>56.69920503031344</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37.98886845973424</v>
+        <v>26.32783339585095</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4763477215251346</v>
+        <v>1.407355390393278</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.860312208092697</v>
+        <v>-0.2966379005540812</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6556</v>
+        <v>6684</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>851.0357595140484</v>
+        <v>862.2108672084934</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>59.69841315770153</v>
+        <v>60.15206109776159</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>40.40427551846406</v>
+        <v>22.21880841004083</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6035759514048381</v>
+        <v>0.7210867208493389</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.028194378965658</v>
+        <v>0.4972067212563968</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6821</v>
+        <v>6579</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>848.5983053794708</v>
+        <v>854.7634772152513</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>67.5</v>
+        <v>163</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.92484296255014</v>
+        <v>57.72249189759273</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.50835099401263</v>
+        <v>37.98886861019259</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.859830537947082</v>
+        <v>0.4763477215251346</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.3237379537184441</v>
+        <v>-1.860312209523657</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6684</v>
+        <v>6556</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>847.2108672084934</v>
+        <v>851.0357595140484</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>49.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>60.15206106605675</v>
+        <v>59.69840479096036</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.21880827809373</v>
+        <v>40.4042754289565</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7210867208493389</v>
+        <v>0.6035759514048381</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4972067216379808</v>
+        <v>0.0281943799959508</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6757</v>
+        <v>6821</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>835.227024654462</v>
+        <v>848.5983053794708</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>56.6</v>
+        <v>67.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.63150805761379</v>
+        <v>58.92484293917131</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.65103432125978</v>
+        <v>27.50835109519987</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.022702465446201</v>
+        <v>2.859830537947082</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.0650093982742934</v>
+        <v>-0.3237379537089002</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6525</v>
+        <v>6757</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>808.670043365829</v>
+        <v>835.227024654462</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>125.5</v>
+        <v>56.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.28865773771665</v>
+        <v>58.63150820476561</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26.62249525061028</v>
+        <v>24.65103428955983</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.3670043365829</v>
+        <v>1.022702465446201</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,11 +1418,11 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.149425658495076</v>
+        <v>-0.06500939911379019</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>800.7147558253639</v>
+        <v>815.7147558253639</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>727</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.47638520201185</v>
+        <v>54.47638519440708</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>29.44735732794548</v>
+        <v>29.44735730816584</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.5714755825363872</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-14.55953599580587</v>
+        <v>-14.55953599551967</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6510</v>
+        <v>6525</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>767.4814070183686</v>
+        <v>808.670043365829</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3610</v>
+        <v>125.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.78316857944371</v>
+        <v>62.28865775585812</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.2238342542197</v>
+        <v>26.62249534797094</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.248140701836861</v>
+        <v>1.3670043365829</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>25.03938460410083</v>
+        <v>-1.149425658704946</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6667</v>
+        <v>6510</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>760.5257221794232</v>
+        <v>782.4814070183686</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>269.5</v>
+        <v>3610</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,29 +1559,29 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>52.36206606816729</v>
+        <v>53.78316857781719</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>16.84875673393351</v>
+        <v>20.22383429553786</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5525722179423138</v>
+        <v>1.248140701836861</v>
       </c>
       <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.3405663301232335</v>
+        <v>25.03938460314617</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>754.5471527858449</v>
+        <v>769.5471527858449</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>77.5</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>67.74840014312406</v>
+        <v>67.74840023336085</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.61544763007293</v>
+        <v>20.61544763463386</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.454715278584495</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.5736951420212004</v>
+        <v>0.5736951416968554</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6654</v>
+        <v>6667</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>752.5760245077367</v>
+        <v>760.5257221794232</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>171.5</v>
+        <v>269.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>80.46472015195955</v>
+        <v>52.36206613609482</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45.04070150092064</v>
+        <v>16.84875690840981</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2576024507736771</v>
+        <v>0.5525722179423138</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.306292569714053</v>
+        <v>-0.340566332603561</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6548</v>
+        <v>6592</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>752.2691627836514</v>
+        <v>757.8405873602951</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>88</v>
+        <v>65.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>67.00594908770033</v>
+        <v>60.42256590439451</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>44.50250952072402</v>
+        <v>28.65069276173388</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2269162783651427</v>
+        <v>0.7840587360295079</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.033515133735808</v>
+        <v>0.5372353388068164</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6592</v>
+        <v>6654</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>742.8405873602951</v>
+        <v>752.5760245077367</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>65.3</v>
+        <v>171.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>60.42256578213127</v>
+        <v>80.46472015195955</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>28.65069286648987</v>
+        <v>45.04070150092064</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7840587360295079</v>
+        <v>0.2576024507736771</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.53723533918841</v>
+        <v>1.306292569714053</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6491</v>
+        <v>6548</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>737.5423075838499</v>
+        <v>752.2691627836514</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>317.5</v>
+        <v>88</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.0654480803446</v>
+        <v>67.00594908770033</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.3332815675027</v>
+        <v>44.50250952072402</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7542307583849934</v>
+        <v>0.2269162783651427</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.015695075438693</v>
+        <v>1.033515133735808</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6756</v>
+        <v>6491</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>730.6638189799498</v>
+        <v>737.5423075838499</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>96.5</v>
+        <v>317.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.95179150283737</v>
+        <v>55.06544815088315</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30.3866490886569</v>
+        <v>34.33328169033648</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5663818979949837</v>
+        <v>0.7542307583849934</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.47888228601655</v>
+        <v>-1.015695076392703</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6598</v>
+        <v>6756</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>709.6707148041402</v>
+        <v>730.6638189799498</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>24.6</v>
+        <v>96.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.20494059159515</v>
+        <v>50.95179156552</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>28.32307820336339</v>
+        <v>30.38664918306646</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4670714804140129</v>
+        <v>0.5663818979949837</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0419988690738708</v>
+        <v>-1.478882286913294</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6811</v>
+        <v>6598</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>699.3644799371708</v>
+        <v>724.6707148041402</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>228.5</v>
+        <v>24.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.76055458355348</v>
+        <v>56.20494077107131</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.12076516880447</v>
+        <v>28.32307825155544</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4364479937170796</v>
+        <v>0.4670714804140129</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.8462737674239493</v>
+        <v>-0.0419988691978853</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6792</v>
+        <v>6811</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>684.9933402053592</v>
+        <v>699.3644799371708</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>67.3</v>
+        <v>228.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.73811702237706</v>
+        <v>55.76055465457666</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>37.25013753392933</v>
+        <v>28.12076531554919</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4993340205359279</v>
+        <v>0.4364479937170796</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.7432289479537149</v>
+        <v>-0.8462737692365163</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6698</v>
+        <v>6792</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>663.1729033366731</v>
+        <v>684.9933402053592</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>38.3</v>
+        <v>67.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>53.8426196014759</v>
+        <v>52.7381170600173</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>36.57107164100541</v>
+        <v>37.25013763724125</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3172903336673161</v>
+        <v>0.4993340205359279</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.3209333130435352</v>
+        <v>-0.7432289481826642</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6488</v>
+        <v>6517</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>662.5458371040457</v>
+        <v>667.392326222285</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>864</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>56.65974066377529</v>
+        <v>57.16659577592073</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.36898300906099</v>
+        <v>27.43225079257473</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2545837104045744</v>
+        <v>2.739232622228495</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-17.74700922377546</v>
+        <v>0.5981459923864278</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6719</v>
+        <v>6698</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>652.6595723008693</v>
+        <v>663.1729033366731</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>219</v>
+        <v>38.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>48.95654425619204</v>
+        <v>53.84261961896203</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>44.33791469534564</v>
+        <v>36.57107168322444</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2659572300869239</v>
+        <v>0.3172903336673161</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-5.562590038960765</v>
+        <v>-0.3209333131770906</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6517</v>
+        <v>6645</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>652.392326222285</v>
+        <v>663.1006352770632</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>14.15</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.1665956167943</v>
+        <v>64.90101595144662</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27.43225059612823</v>
+        <v>32.31940522663895</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.739232622228495</v>
+        <v>1.310063527706323</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.5981459935884297</v>
+        <v>0.251348291862683</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6570</v>
+        <v>6589</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>650.8031252206774</v>
+        <v>660.9019786625693</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>57.3</v>
+        <v>44.85</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>59.77254341092335</v>
+        <v>50.6570034606313</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.9166361236684</v>
+        <v>22.66791572919002</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5803125220677403</v>
+        <v>0.5901978662569263</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.6655729637598826</v>
+        <v>0.4747154915190935</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6651</v>
+        <v>6719</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>648.8858167046538</v>
+        <v>652.6595723008693</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.14167399444454</v>
+        <v>48.9565442629027</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>34.6185157097875</v>
+        <v>44.33791476595877</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3885816704653897</v>
+        <v>0.2659572300869239</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-2.950196966813663</v>
+        <v>-5.562590039628549</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6645</v>
+        <v>6570</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>648.1006352770632</v>
+        <v>650.8031252206774</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>14.15</v>
+        <v>57.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>64.90101592564318</v>
+        <v>59.77254346644195</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.31940522847853</v>
+        <v>26.91663635538671</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.310063527706323</v>
+        <v>0.5803125220677403</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.2513482919771603</v>
+        <v>-0.6655729641033075</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6589</v>
+        <v>6651</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>645.9019786625693</v>
+        <v>648.8858167046538</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>44.85</v>
+        <v>133</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.65700329549494</v>
+        <v>52.14167402483105</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>22.6679157040895</v>
+        <v>34.61851590239014</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5901978662569263</v>
+        <v>0.3885816704653897</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,11 +2478,11 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4747154919960829</v>
+        <v>-2.950196967500529</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
         <v>55.53310866169349</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>50.48535183839749</v>
+        <v>50.48535206545</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.4189708026942879</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-1.223512062722292</v>
+        <v>-1.22351206279861</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.96174772500873</v>
+        <v>47.96174784543928</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21.20110146576823</v>
+        <v>21.20110146615447</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.3340268944110297</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.112766244970513</v>
+        <v>-1.112766245962654</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>46.60391911769435</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>19.06212519924883</v>
+        <v>19.06212538316808</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.5824519500867729</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.549315092358835</v>
+        <v>-3.54931509321742</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>584.8638308245222</v>
+        <v>599.8638308245222</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>141</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.14067556295032</v>
+        <v>55.14067572581006</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.25758543903784</v>
+        <v>24.25758559278696</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.486383082452225</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2251675362661762</v>
+        <v>0.2251675344536257</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>43.2512782530456</v>
+        <v>43.2512782626123</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20.11531736264052</v>
+        <v>20.11531746993367</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7089895119201105</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-11.18862285771298</v>
+        <v>-11.18862285895303</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.57687357115028</v>
+        <v>51.5768735752023</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>8.177603659249908</v>
+        <v>8.177603675409113</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>2.521518987341772</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-2.088633093048997</v>
+        <v>-2.08863309333519</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6531</v>
+        <v>6763</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>575.7228081680405</v>
+        <v>576.0552387367616</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>932</v>
+        <v>48.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.45569100974881</v>
+        <v>57.29975265395449</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>26.21777000390197</v>
+        <v>25.54139709061766</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5722808168040465</v>
+        <v>0.60552387367615</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-33.45027429296295</v>
+        <v>0.5138148650215691</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6690</v>
+        <v>6531</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>573.9901359742596</v>
+        <v>575.7228081680405</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>175.5</v>
+        <v>932</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>52.58693386197238</v>
+        <v>47.45569101402066</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.8510034838432</v>
+        <v>26.21777010402383</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.399013597425967</v>
+        <v>0.5722808168040465</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.4135000890572087</v>
+        <v>-33.45027429429851</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6658</v>
+        <v>6690</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>570.8810970695561</v>
+        <v>573.9901359742596</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>171.5</v>
+        <v>175.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.89151977327095</v>
+        <v>52.58693394769862</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>40.64749410518068</v>
+        <v>20.85100372427834</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5881097069556086</v>
+        <v>1.399013597425967</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-7.881722618659072</v>
+        <v>-0.4135000899157939</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6716</v>
+        <v>6658</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>564.5636299120681</v>
+        <v>570.8810970695561</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>171.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45.59213573547009</v>
+        <v>44.8915197891732</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>34.06645631654469</v>
+        <v>40.64749429613038</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4563629912068122</v>
+        <v>0.5881097069556086</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-2.760443362193044</v>
+        <v>-7.881722619460412</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6669</v>
+        <v>6716</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>564.2916378359471</v>
+        <v>564.5636299120681</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>4850</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>43.40036561299445</v>
+        <v>45.59213574163049</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22.725692198122</v>
+        <v>34.06645659936385</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9291637835947152</v>
+        <v>0.4563629912068122</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-103.3916907951734</v>
+        <v>-2.760443362574632</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6805</v>
+        <v>6669</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>563.7958297853377</v>
+        <v>564.2916378359471</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1825</v>
+        <v>4850</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>46.91564593638572</v>
+        <v>43.40036560650229</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.67032824561152</v>
+        <v>22.72569235659354</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8795829785337754</v>
+        <v>0.9291637835947152</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-15.76731125583796</v>
+        <v>-103.3916908037596</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6526</v>
+        <v>6805</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>562.8539316896206</v>
+        <v>563.7958297853377</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>633</v>
+        <v>1825</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.49856695574925</v>
+        <v>46.91564596303309</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.9411600212376</v>
+        <v>15.67032860195372</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2853931689620547</v>
+        <v>0.8795829785337754</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-12.98589358143292</v>
+        <v>-15.76731126375588</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6763</v>
+        <v>6526</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>561.0552387367616</v>
+        <v>562.8539316896206</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>48.2</v>
+        <v>633</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>57.29975266106455</v>
+        <v>46.4985669567825</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25.54139702538401</v>
+        <v>18.94116009116274</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.60552387367615</v>
+        <v>0.2853931689620547</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,11 +3220,11 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.513814865460392</v>
+        <v>-12.98589358400863</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>545.4950742719509</v>
+        <v>560.4950742719509</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>421</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.19460400248141</v>
+        <v>49.19460402550239</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>11.23759351473349</v>
+        <v>11.23759364451204</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.049507427195091</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.2415158755552601</v>
+        <v>-0.2415158772723954</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>529.3554342984144</v>
+        <v>544.3554342984144</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>91.59999999999999</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.70982249502863</v>
+        <v>54.70982241645781</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.57660021993369</v>
+        <v>24.57660027552157</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.935543429841438</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4542332045452708</v>
+        <v>0.4542332043544697</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>526.6321217361667</v>
+        <v>541.6321217361667</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>19.65</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.36920026014556</v>
+        <v>52.36920024245772</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5.911962760106038</v>
+        <v>5.911962663137474</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.6632121736166775</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.37661962781556</v>
+        <v>49.37661960476582</v>
       </c>
       <c r="I56" s="2" t="n">
         <v>12.81085826791085</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-1.098763745639067</v>
+        <v>-1.098763745925257</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.79220317319079</v>
+        <v>49.7922032030588</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.71884541123137</v>
+        <v>26.71884551146981</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.4428390904403546</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.3072782284817903</v>
+        <v>-0.3072782287584434</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.44517605790305</v>
+        <v>46.44517608196516</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>29.99651366647329</v>
+        <v>29.9965138015354</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.4156033236241881</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.166016209500364</v>
+        <v>-1.16601620997734</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.11915252893135</v>
+        <v>48.11915256730837</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>35.92467703639542</v>
+        <v>35.92467723739604</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.5707539690714033</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.10552091339119</v>
+        <v>-1.10552091385863</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>42.10265693666164</v>
+        <v>42.10265696163322</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.91734190435798</v>
+        <v>22.91734206677069</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.4243808941134514</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-2.022874381984886</v>
+        <v>-2.022874382538195</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.68087870212055</v>
+        <v>39.68087871128064</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.96610303302254</v>
+        <v>20.96610318341047</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.3268048270922885</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-2.654046584841903</v>
+        <v>-2.654046584985004</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.21659418919258</v>
+        <v>45.21659420321429</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24.40252175594362</v>
+        <v>24.40252190714546</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.2678328655079979</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.451562530512254</v>
+        <v>-2.451562531180014</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>46.20428115430055</v>
+        <v>46.20428116721558</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>25.57560206181457</v>
+        <v>25.57560212782932</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.2111316045162621</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.243346258314066</v>
+        <v>-1.243346258571637</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.25893329713213</v>
+        <v>52.25893339507093</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.78344425100876</v>
+        <v>12.78344441448273</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.2586417442424168</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.055099372385292</v>
+        <v>-0.0550993727478005</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6505</v>
+        <v>6720</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>481.1424424836221</v>
+        <v>482.0174326872307</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>52.8</v>
+        <v>149</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.16808277476873</v>
+        <v>40.5230717460269</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.07561188610444</v>
+        <v>29.37418397648771</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6142442483622089</v>
+        <v>1.701743268723073</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0041492022471386</v>
+        <v>0.262928896358634</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6840</v>
+        <v>6505</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>479.1672047976848</v>
+        <v>481.1424424836221</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.75859208884497</v>
+        <v>50.16808280536309</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.54206511084317</v>
+        <v>14.07561195435353</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4167204797684722</v>
+        <v>0.6142442483622089</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0203002668135018</v>
+        <v>-0.0041492023806964</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6790</v>
+        <v>6840</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>478.3415831853125</v>
+        <v>479.1672047976848</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>39.65</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.79785433227166</v>
+        <v>51.75859091040773</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.5214021550435</v>
+        <v>19.54206450203678</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.8341583185312523</v>
+        <v>0.4167204797684722</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0361937583789387</v>
+        <v>0.0203002743594209</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6781</v>
+        <v>6790</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>478.1811518884475</v>
+        <v>478.3415831853125</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1145</v>
+        <v>39.65</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.63762302090735</v>
+        <v>50.79785426344304</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>13.73770392735597</v>
+        <v>14.52140227822355</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8181151888447532</v>
+        <v>0.8341583185312523</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-7.933351130968696</v>
+        <v>0.0361937582739998</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6706</v>
+        <v>6781</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>475.1373996284708</v>
+        <v>478.1811518884475</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>167</v>
+        <v>1145</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.44262441353825</v>
+        <v>49.63762303308128</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>22.36519026262853</v>
+        <v>13.737703984098</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.013739962847086</v>
+        <v>0.8181151888447532</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-5.942435776148383</v>
+        <v>-7.933351134975198</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6720</v>
+        <v>6706</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>467.0174326872307</v>
+        <v>475.1373996284708</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>40.52307160250571</v>
+        <v>45.44262443065707</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.37418386912381</v>
+        <v>22.36519040613975</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.701743268723073</v>
+        <v>1.013739962847086</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,11 +4174,11 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2629288976941977</v>
+        <v>-5.942435776892459</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>39.25559386739774</v>
+        <v>39.25559394145173</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.2648046122588</v>
+        <v>16.26480467281996</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.2634133870419619</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.5787530688384424</v>
+        <v>-0.5787530691246392</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.76427001385105</v>
+        <v>52.76426996618001</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.54654471552102</v>
+        <v>20.54654472876085</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.4581553744779025</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2356214716549104</v>
+        <v>0.2356214712733302</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>50.23962001129429</v>
+        <v>50.23962041936791</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.13141559676797</v>
+        <v>13.13141592515555</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.8150136925321049</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1441564081256232</v>
+        <v>-0.1441564089842061</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>42.57933049912814</v>
+        <v>42.57933055061595</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>39.32751119829831</v>
+        <v>39.32751134296387</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.4947907351969416</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-5.045702315905707</v>
+        <v>-5.045702316611648</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>39.91318917835019</v>
+        <v>39.91318918880957</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.62527288055928</v>
+        <v>16.62527290986407</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.4446545196751592</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-4.902687506993615</v>
+        <v>-4.902687507661407</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.14137732558691</v>
+        <v>50.14137737095711</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.74869765195773</v>
+        <v>15.74869768822829</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.3928489875933674</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1458989299583265</v>
+        <v>-0.1458989300537246</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.49490369077849</v>
+        <v>48.49490328340741</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19.87968205224712</v>
+        <v>19.87968210284658</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.6995811258009268</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0088074261618304</v>
+        <v>-0.008807426047355999</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4555,21 +4555,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6715</v>
+        <v>6743</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>434.9793069394556</v>
+        <v>429.3169211907812</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>391.5</v>
+        <v>28.9</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,49 +4580,49 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.31091326738201</v>
+        <v>48.31901999660622</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.16714667046929</v>
+        <v>23.80706252899326</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.497930693945564</v>
+        <v>1.431692119078114</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-11.78991338669432</v>
+        <v>-0.19491880474203</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6743</v>
+        <v>6614</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>429.3169211907812</v>
+        <v>425.6582175271963</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>28.9</v>
+        <v>39.95</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>48.31901987002738</v>
+        <v>48.82386085379048</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>23.80706240214526</v>
+        <v>11.88607727449661</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.431692119078114</v>
+        <v>1.065821752719626</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1949188045703139</v>
+        <v>0.1312034271422947</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6614</v>
+        <v>6754</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>425.6582175271963</v>
+        <v>416.1587073224381</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>39.95</v>
+        <v>45</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.82386107845721</v>
+        <v>50.09880413356717</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.8860772744966</v>
+        <v>21.64506506988988</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.065821752719626</v>
+        <v>0.6158707322438157</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1312034268847282</v>
+        <v>0.0393476784818668</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6754</v>
+        <v>6679</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>416.1587073224381</v>
+        <v>412.2506625879463</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>45</v>
+        <v>268</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.09880403299931</v>
+        <v>39.18959696828557</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>21.64506510419005</v>
+        <v>27.7300840318875</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6158707322438157</v>
+        <v>0.2250662587946274</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0393476786535822</v>
+        <v>-7.045084506825816</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6679</v>
+        <v>6664</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>412.2506625879463</v>
+        <v>408.0412511600979</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>268</v>
+        <v>368</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>39.1895969616655</v>
+        <v>36.78254955190035</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>27.73008400009535</v>
+        <v>23.10328653578096</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2250662587946274</v>
+        <v>0.3041251160097865</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-7.045084505490188</v>
+        <v>-8.820433614817933</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6664</v>
+        <v>6584</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>408.0412511600979</v>
+        <v>404.5842300312814</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>368</v>
+        <v>585</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>36.78254951941623</v>
+        <v>40.57023164502741</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.10328626672168</v>
+        <v>13.03790063600219</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3041251160097865</v>
+        <v>0.4584230031281394</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-8.820433612814597</v>
+        <v>-13.90060534229163</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6584</v>
+        <v>6782</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>404.5842300312814</v>
+        <v>404.3080260394906</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>585</v>
+        <v>194.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.57023162851407</v>
+        <v>46.28656706916178</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.03790041954738</v>
+        <v>10.2095207001832</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4584230031281394</v>
+        <v>0.4308026039490564</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-13.90060534095607</v>
+        <v>0.5644329024276584</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6782</v>
+        <v>6799</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>404.3080260394906</v>
+        <v>403.2779871882066</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>194.5</v>
+        <v>86.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.28656693710408</v>
+        <v>38.70575491876673</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10.2095205087155</v>
+        <v>34.3400865993091</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4308026039490564</v>
+        <v>0.3277987188206648</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>1</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.5644329037632123</v>
+        <v>-2.899765832374634</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6799</v>
+        <v>6776</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>403.2779871882066</v>
+        <v>401.2488834612473</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>86.5</v>
+        <v>59.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.70575486505143</v>
+        <v>50.87379045635567</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>34.34008660844145</v>
+        <v>11.23371575282052</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3277987188206648</v>
+        <v>0.6248883461247342</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-2.899765831401588</v>
+        <v>0.0225117481222518</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6776</v>
+        <v>6741</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>401.2488834612473</v>
+        <v>376.9510376099445</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>59.5</v>
+        <v>62.6</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.87379043725076</v>
+        <v>47.62584923475983</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.23371571298776</v>
+        <v>12.08359956682818</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6248883461247342</v>
+        <v>0.6951037609944519</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0225117482176466</v>
+        <v>-0.1669665498339222</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6741</v>
+        <v>6582</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>376.9510376099445</v>
+        <v>374.9236742020545</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>62.6</v>
+        <v>31.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.62584923967975</v>
+        <v>53.1599826360624</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.08359955888562</v>
+        <v>21.93053159316065</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6951037609944519</v>
+        <v>0.492367420205457</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1669665497385297</v>
+        <v>0.0521510105015865</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6582</v>
+        <v>6591</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>374.9236742020545</v>
+        <v>373.9439237735078</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>31.5</v>
+        <v>55.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.15998241994541</v>
+        <v>46.71509235069598</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.93053144069051</v>
+        <v>22.26856670675994</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.492367420205457</v>
+        <v>0.3943923773507808</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0521510107973183</v>
+        <v>-0.02956936590911</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6591</v>
+        <v>6486</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>373.9439237735078</v>
+        <v>364.8750285419753</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>55.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.71509230387012</v>
+        <v>42.71968894737202</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.26856665412213</v>
+        <v>21.42589043556209</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3943923773507808</v>
+        <v>0.4875028541975337</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0295693655466036</v>
+        <v>0.0648897474618612</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6486</v>
+        <v>6806</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>364.8750285419753</v>
+        <v>359.2921863408052</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>4.04</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.71968877708849</v>
+        <v>31.90654383687047</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>21.42589010370338</v>
+        <v>30.99666403825202</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4875028541975337</v>
+        <v>0.4292186340805172</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0648897479006996</v>
+        <v>0.3543742163207071</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6806</v>
+        <v>6796</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>359.2921863408052</v>
+        <v>350.4606801793023</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>4.04</v>
+        <v>58.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>31.90654378221178</v>
+        <v>37.50204374688793</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>30.99666397998374</v>
+        <v>33.23532305654146</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4292186340805172</v>
+        <v>0.546068017930228</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.3543742169312498</v>
+        <v>0.06791982061699769</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6796</v>
+        <v>6588</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>350.4606801793023</v>
+        <v>344.168681724904</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>58.8</v>
+        <v>102</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>37.50204378798177</v>
+        <v>35.54215914371426</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>33.23532302869783</v>
+        <v>20.50098885856067</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.546068017930228</v>
+        <v>0.9168681724904042</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0679198204262037</v>
+        <v>-1.588524280442563</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6588</v>
+        <v>6560</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>344.168681724904</v>
+        <v>343.2712129146701</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>35.54215913263459</v>
+        <v>40.92673473239544</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>20.50098875528046</v>
+        <v>15.56015488132203</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9168681724904042</v>
+        <v>0.8271212914670065</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.588524280213617</v>
+        <v>-0.1896645404116896</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6560</v>
+        <v>6753</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>343.2712129146701</v>
+        <v>342.7867770384262</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.92673478009271</v>
+        <v>38.72653749524746</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.56015481958014</v>
+        <v>13.05630223158154</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8271212914670065</v>
+        <v>0.2786777038426252</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1896645402495086</v>
+        <v>-0.273120032443956</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6753</v>
+        <v>6727</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>342.7867770384262</v>
+        <v>340.2137905907762</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>120</v>
+        <v>399</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>38.7265374577003</v>
+        <v>38.29042432157867</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.05630213151427</v>
+        <v>24.34106674420586</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2786777038426252</v>
+        <v>0.5213790590776215</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2731200319669602</v>
+        <v>-25.44031596450131</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6727</v>
+        <v>6715</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>340.2137905907762</v>
+        <v>339.9793069394556</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>399</v>
+        <v>391.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.2904243202285</v>
+        <v>42.31091327684112</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>24.34106668050701</v>
+        <v>23.1671467711225</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5213790590776215</v>
+        <v>0.497930693945564</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,11 +5605,11 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-25.44031596406248</v>
+        <v>-11.78991338764828</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.56046524725676</v>
+        <v>40.5604652939291</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.96860127374476</v>
+        <v>20.96860132375383</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.3379542727107101</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-3.895956947657988</v>
+        <v>-3.89595695061529</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>42.70609586530189</v>
+        <v>42.70609587153491</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.00438322937508</v>
+        <v>13.00438332645964</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.7608223753026472</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-10.58167931324792</v>
+        <v>-10.58167931525106</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.74771925044959</v>
+        <v>41.74771930168982</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.00912796952439</v>
+        <v>14.00912810878107</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.4589455598620885</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.802423777776995</v>
+        <v>-1.802423778149052</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.23292442507556</v>
+        <v>44.23292447833776</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.35415914732986</v>
+        <v>16.35415918657088</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.3376620135339795</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1166041021153721</v>
+        <v>-0.1166041028022341</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.28762453691233</v>
+        <v>45.28762458171081</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>30.98027017047518</v>
+        <v>30.9802703042783</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.2722022442105728</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3778172842952344</v>
+        <v>-0.3778172846863656</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>32.02842565642543</v>
+        <v>32.02842536162986</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>36.70445675178912</v>
+        <v>36.70445680198007</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.4621981492783083</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0787579622125012</v>
+        <v>0.0787579623937555</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>42.85298511199251</v>
+        <v>42.85298519105631</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.99805650069054</v>
+        <v>15.99805643560493</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.2183585170196137</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.2069758632277131</v>
+        <v>-0.2069758634280505</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>38.17081093300406</v>
+        <v>38.17081100860877</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>25.31596515884792</v>
+        <v>25.31596511571346</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.2983459147424511</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-3.187205407847617</v>
+        <v>-3.18720540946936</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45.32758058682212</v>
+        <v>45.3275807536074</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.03816551999384</v>
+        <v>18.03816561977464</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.9134955456336898</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0988056528788671</v>
+        <v>0.09880565272623271</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>34.65905129818704</v>
+        <v>34.65905130779292</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>26.66259027819535</v>
+        <v>26.66259043203078</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.566970931389577</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-29.50388463613598</v>
+        <v>-29.50388463957033</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.38488594806845</v>
+        <v>47.38488606810876</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17.35437898483762</v>
+        <v>17.35437902560248</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.5408384706745388</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0120363957732418</v>
+        <v>-0.0120363962693078</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.17555397773148</v>
+        <v>42.17555421804433</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>26.80314266072943</v>
+        <v>26.80314249141934</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.7797489702591379</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.2722332480637313</v>
+        <v>0.2722332476821448</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>32.05321326489768</v>
+        <v>32.05321326863863</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.92944573009581</v>
+        <v>18.92944589645646</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>1.014808867285957</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-23.75395925585467</v>
+        <v>-23.75395925671326</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>29.50880640363182</v>
+        <v>29.508806410909</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>22.56580683122496</v>
+        <v>22.56580686214042</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.3419067588365156</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.156191030053747</v>
+        <v>-1.156191030225462</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>33.8375275201508</v>
+        <v>33.83752760657266</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>23.993351329605</v>
+        <v>23.99335142613947</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.4816909636133307</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-15.8073570539635</v>
+        <v>-15.80735706102293</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>34.89053250460802</v>
+        <v>34.89053252341523</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>24.55747221299236</v>
+        <v>24.55747237557445</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.3713342504241423</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-5.544018983341582</v>
+        <v>-5.544018984238299</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.62034853849859</v>
+        <v>45.62034857662661</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.94188699733569</v>
+        <v>18.94188707420411</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.303387280682273</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.6755486153582034</v>
+        <v>-0.6755486154917597</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>33.87017950631197</v>
+        <v>33.87017961844943</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.4359650171781</v>
+        <v>12.4359652174477</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.5563077846759226</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.026731542109003</v>
+        <v>0.0267315418991307</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.02740809136308</v>
+        <v>38.02740809896245</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19.43003087051283</v>
+        <v>19.43003102963046</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.5998069785749578</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-35.93674722678978</v>
+        <v>-35.93674722974703</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6835</v>
+        <v>6624</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>216.5139668567862</v>
+        <v>228.2826100753282</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>36.45</v>
+        <v>42.95</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>40.21757428699651</v>
+        <v>49.7651739035207</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>11.84936842105753</v>
+        <v>12.78802332199968</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.1513966856786202</v>
+        <v>0.3282610075328188</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.2202401640833645</v>
+        <v>1.196900092381604</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6692</v>
+        <v>6835</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>215.9797119328594</v>
+        <v>216.5139668567862</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>25.15</v>
+        <v>36.45</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>31.17327505361293</v>
+        <v>40.2175743820094</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>25.54810292523056</v>
+        <v>11.84936850189171</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5979711932859375</v>
+        <v>0.1513966856786202</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0357561056390496</v>
+        <v>-0.2202401643027765</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6624</v>
+        <v>6692</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>213.2826100753282</v>
+        <v>215.9797119328594</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>42.95</v>
+        <v>25.15</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.76517388607422</v>
+        <v>31.17327506010433</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.78802328932573</v>
+        <v>25.54810293174533</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.3282610075328188</v>
+        <v>0.5979711932859375</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,11 +6771,11 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>1.196900092629635</v>
+        <v>-0.0357561057058293</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.81324753269506</v>
+        <v>39.81324755819395</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.41020811668674</v>
+        <v>15.41020817423257</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.7944647586484911</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-2.461666938478563</v>
+        <v>-2.461666939337125</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>44.57433337164276</v>
+        <v>44.57433336584746</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.33269621905639</v>
+        <v>12.33269624474791</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>1.131589454013918</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0613888653100068</v>
+        <v>-0.0613888653290758</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>29.69263671653396</v>
+        <v>29.69263674142522</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.69284032437168</v>
+        <v>17.69284033354296</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.4807951861069746</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0926751667173485</v>
+        <v>-0.0926751670416998</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>49.17416285415418</v>
+        <v>49.1741628585952</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.70589858380092</v>
+        <v>15.70589865101595</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.3922253583504528</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.07366923592527851</v>
+        <v>0.0736692359157433</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>33.41985837213251</v>
+        <v>33.41985843911156</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.38870414897994</v>
+        <v>17.38870420291641</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.8590318295646184</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.4162624397911492</v>
+        <v>-0.4162624403444561</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>29.37125706602235</v>
+        <v>29.37125708994841</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>14.79088887781482</v>
+        <v>14.79088885947381</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.8014550483151721</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0122163748732506</v>
+        <v>-0.0122163748350914</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>41.07953107765963</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.02671384896492</v>
+        <v>19.02671386249477</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.2207261891623441</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.06612593847954019</v>
+        <v>-0.0661259385081595</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
